--- a/src/main/java/com/NonKeyword_FutureReadyFramework/automation/config/Config.xlsx
+++ b/src/main/java/com/NonKeyword_FutureReadyFramework/automation/config/Config.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23801"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{941CC255-8867-4D3E-ABD5-206CFBD03BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56022848-3367-4E34-83A0-EE5730C75C95}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="configdata" sheetId="4" r:id="rId1"/>
@@ -87,7 +87,7 @@
     <t>Test123$</t>
   </si>
   <si>
-    <t>https://www.office.fedex.com/</t>
+    <t>https://staging2.office.fedex.com</t>
   </si>
 </sst>
 </file>
@@ -441,14 +441,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6E5789C-42AE-4E65-B5B7-90544D508AC3}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="3"/>
-    <col min="2" max="2" width="11.44140625" style="3" customWidth="1"/>
-    <col min="3" max="16384" width="9.109375" style="3"/>
+    <col min="1" max="1" width="9.08984375" style="3"/>
+    <col min="2" max="2" width="11.453125" style="3" customWidth="1"/>
+    <col min="3" max="16384" width="9.08984375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -459,7 +459,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -470,7 +470,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -481,7 +481,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -493,7 +493,7 @@
         <v>Test123$</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -529,13 +529,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="17.33203125" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" customWidth="1"/>
+    <col min="2" max="2" width="17.36328125" customWidth="1"/>
+    <col min="3" max="3" width="19.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -546,7 +546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -557,7 +557,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -568,7 +568,7 @@
         <v>4416279</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -579,7 +579,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -614,12 +614,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE1F85C0-43B7-4429-9B1E-A7EC675C8395}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="16384" width="9.109375" style="3"/>
+    <col min="1" max="16384" width="9.08984375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -627,7 +627,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
@@ -635,17 +635,17 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B6" s="3" t="s">
         <v>10</v>
       </c>

--- a/src/main/java/com/NonKeyword_FutureReadyFramework/automation/config/Config.xlsx
+++ b/src/main/java/com/NonKeyword_FutureReadyFramework/automation/config/Config.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23801"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56022848-3367-4E34-83A0-EE5730C75C95}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686F9841-D9C4-4A0B-9E90-5835EBEF9018}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/src/main/java/com/NonKeyword_FutureReadyFramework/automation/config/Config.xlsx
+++ b/src/main/java/com/NonKeyword_FutureReadyFramework/automation/config/Config.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686F9841-D9C4-4A0B-9E90-5835EBEF9018}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484BFF66-36E8-4E38-9390-D5B54DAE7079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="configdata" sheetId="4" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="26">
   <si>
     <t>Sl.No</t>
   </si>
@@ -88,6 +88,27 @@
   </si>
   <si>
     <t>https://staging2.office.fedex.com</t>
+  </si>
+  <si>
+    <t>https://staging3.office.fedex.com</t>
+  </si>
+  <si>
+    <t>https://office.fedex.com</t>
+  </si>
+  <si>
+    <t>Stage3</t>
+  </si>
+  <si>
+    <t>Stage2</t>
+  </si>
+  <si>
+    <t>Prod</t>
+  </si>
+  <si>
+    <t>Staging</t>
+  </si>
+  <si>
+    <t>https://staging.office.fedex.com</t>
   </si>
 </sst>
 </file>
@@ -440,15 +461,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6E5789C-42AE-4E65-B5B7-90544D508AC3}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.08984375" style="3"/>
-    <col min="2" max="2" width="11.453125" style="3" customWidth="1"/>
-    <col min="3" max="16384" width="9.08984375" style="3"/>
+    <col min="1" max="1" width="9.109375" style="3"/>
+    <col min="2" max="2" width="11.44140625" style="3" customWidth="1"/>
+    <col min="3" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -459,7 +480,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -470,7 +491,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -481,7 +502,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -493,7 +514,7 @@
         <v>Test123$</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -502,6 +523,50 @@
       </c>
       <c r="C5" s="3" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -529,13 +594,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.36328125" customWidth="1"/>
-    <col min="3" max="3" width="19.54296875" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -546,7 +611,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -557,7 +622,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -568,7 +633,7 @@
         <v>4416279</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -579,7 +644,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -613,13 +678,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE1F85C0-43B7-4429-9B1E-A7EC675C8395}">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="9.08984375" style="3"/>
+    <col min="1" max="1" width="11.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -627,7 +693,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
@@ -635,20 +701,29 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B8" s="5"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B9" s="5"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B10" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/main/java/com/NonKeyword_FutureReadyFramework/automation/config/Config.xlsx
+++ b/src/main/java/com/NonKeyword_FutureReadyFramework/automation/config/Config.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484BFF66-36E8-4E38-9390-D5B54DAE7079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7822E336-CCB5-4112-9697-33BD395E32AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13,6 +13,7 @@
     <sheet name="Data" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -488,7 +489,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">

--- a/src/main/java/com/NonKeyword_FutureReadyFramework/automation/config/Config.xlsx
+++ b/src/main/java/com/NonKeyword_FutureReadyFramework/automation/config/Config.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7822E336-CCB5-4112-9697-33BD395E32AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C15964BA-F439-4918-BC7B-D93F791C82CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13,7 +13,6 @@
     <sheet name="Data" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -489,7 +488,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">

--- a/src/main/java/com/NonKeyword_FutureReadyFramework/automation/config/Config.xlsx
+++ b/src/main/java/com/NonKeyword_FutureReadyFramework/automation/config/Config.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C15964BA-F439-4918-BC7B-D93F791C82CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A699532-0C8E-48A2-B22B-E254F8ABD7CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -488,7 +488,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">
